--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484761_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484761_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.7095</v>
+        <v>8.7287</v>
       </c>
       <c r="E2" t="n">
-        <v>7.8163</v>
+        <v>5.9466</v>
       </c>
       <c r="F2" t="n">
-        <v>3.8932</v>
+        <v>2.7821</v>
       </c>
       <c r="G2" t="n">
         <v>2.0563</v>
@@ -610,13 +610,13 @@
         <v>3.0192</v>
       </c>
       <c r="S2" t="n">
-        <v>5.1061</v>
+        <v>2.1252</v>
       </c>
       <c r="T2" t="n">
-        <v>3.8103</v>
+        <v>1.9405</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2958</v>
+        <v>0.1847</v>
       </c>
       <c r="V2" t="n">
         <v>2.4714</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.8987</v>
+        <v>4.0213</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1743</v>
+        <v>2.3764</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7243</v>
+        <v>1.645</v>
       </c>
       <c r="G3" t="n">
         <v>0.8682</v>
@@ -688,13 +688,13 @@
         <v>2.6418</v>
       </c>
       <c r="S3" t="n">
-        <v>1.9176</v>
+        <v>1.0402</v>
       </c>
       <c r="T3" t="n">
-        <v>2.1555</v>
+        <v>1.3575</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.238</v>
+        <v>-0.3173</v>
       </c>
       <c r="V3" t="n">
         <v>3.4338</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0631</v>
+        <v>3.3137</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1449</v>
+        <v>3.2368</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0818</v>
+        <v>0.0769</v>
       </c>
       <c r="G4" t="n">
         <v>-0.2779</v>
@@ -766,13 +766,13 @@
         <v>2.0757</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7912</v>
+        <v>0.4594</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5139</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2774</v>
+        <v>-0.1187</v>
       </c>
       <c r="V4" t="n">
         <v>1.2452</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V. MARTÍN SORIANO</t>
+          <t>N. ALBALADEJO PEREZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.317</v>
+        <v>0.6728</v>
       </c>
       <c r="E5" t="n">
-        <v>0.317</v>
+        <v>-0.3224</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>0.9953</v>
       </c>
       <c r="G5" t="n">
-        <v>0.317</v>
+        <v>-0.4427</v>
       </c>
       <c r="H5" t="n">
-        <v>0.317</v>
+        <v>2.7594</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>-3.2021</v>
       </c>
       <c r="J5" t="n">
-        <v>0.317</v>
+        <v>-0.7118</v>
       </c>
       <c r="K5" t="n">
-        <v>0.317</v>
+        <v>2.4041</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-3.1159</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>0.2691</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.3553</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-0.0863</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.9435</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.1322</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.0757</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>0.7756999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.5216</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0.7459</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. ALBALADEJO PEREZ</t>
+          <t>V. MARTÍN SORIANO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1282</v>
+        <v>0.317</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5760999999999999</v>
+        <v>0.317</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7043</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.4427</v>
+        <v>0.317</v>
       </c>
       <c r="H6" t="n">
-        <v>2.7594</v>
+        <v>0.317</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.2021</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.7118</v>
+        <v>0.317</v>
       </c>
       <c r="K6" t="n">
-        <v>2.4041</v>
+        <v>0.317</v>
       </c>
       <c r="L6" t="n">
-        <v>-3.1159</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2691</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3553</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0863</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9435</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1322</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0757</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.231</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>1.2679</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.0369</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0438</v>
+        <v>0.302</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.8877</v>
+        <v>-1.8675</v>
       </c>
       <c r="F7" t="n">
-        <v>1.9315</v>
+        <v>2.1696</v>
       </c>
       <c r="G7" t="n">
         <v>-1.8019</v>
@@ -1000,13 +1000,13 @@
         <v>0.9435</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1352</v>
+        <v>0.123</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1916</v>
+        <v>0.2117</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3268</v>
+        <v>-0.0887</v>
       </c>
       <c r="V7" t="n">
         <v>2.1696</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>V. MARTIN SORIANO</t>
+          <t>S. GALVEZ ARROYO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.1077</v>
+        <v>-1.1257</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5101</v>
+        <v>-0.7503</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.5976</v>
+        <v>-0.3753</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3056</v>
+        <v>-4.2133</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0626</v>
+        <v>-0.8491</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3682</v>
+        <v>-3.3641</v>
       </c>
       <c r="J8" t="n">
-        <v>0.08450000000000001</v>
+        <v>-3.1827</v>
       </c>
       <c r="K8" t="n">
-        <v>0.08450000000000001</v>
+        <v>-0.749</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-2.4337</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2211</v>
+        <v>-1.0306</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1471</v>
+        <v>-0.1001</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3682</v>
+        <v>-0.9304</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.6983</v>
+        <v>0.5661</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.0757</v>
+        <v>-1.887</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3774</v>
+        <v>2.4531</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1528</v>
+        <v>-0.2707</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1793</v>
+        <v>0.6027</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0264</v>
+        <v>-0.8735000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.8678</v>
+        <v>2.7922</v>
       </c>
       <c r="W8" t="n">
-        <v>0.3018</v>
+        <v>3.7166</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.1696</v>
+        <v>-0.9244</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. GALVEZ ARROYO</t>
+          <t>V. MARTIN SORIANO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.3674</v>
+        <v>-3.0548</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.6217</v>
+        <v>-1.5101</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7457</v>
+        <v>-1.5447</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.2133</v>
+        <v>0.3056</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8491</v>
+        <v>-0.0626</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.3641</v>
+        <v>0.3682</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.1827</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.749</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.4337</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.0306</v>
+        <v>0.2211</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1001</v>
+        <v>-0.1471</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9304</v>
+        <v>0.3682</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5661</v>
+        <v>-1.6983</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.887</v>
+        <v>-2.0757</v>
       </c>
       <c r="R9" t="n">
-        <v>2.4531</v>
+        <v>0.3774</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.5125</v>
+        <v>0.2058</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.2687</v>
+        <v>0.1793</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.2438</v>
+        <v>0.0265</v>
       </c>
       <c r="V9" t="n">
-        <v>2.7922</v>
+        <v>-1.8678</v>
       </c>
       <c r="W9" t="n">
-        <v>3.7166</v>
+        <v>0.3018</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.9244</v>
+        <v>-2.1696</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.2642</v>
+        <v>-3.8724</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.9542</v>
+        <v>-3.6418</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.31</v>
+        <v>-0.2307</v>
       </c>
       <c r="G10" t="n">
         <v>-2.466</v>
@@ -1234,13 +1234,13 @@
         <v>1.5096</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1946</v>
+        <v>0.1972</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3498</v>
+        <v>-0.0374</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1552</v>
+        <v>0.2346</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2262</v>
@@ -1267,22 +1267,22 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>8.420999999999999</v>
+        <v>9.302599999999998</v>
       </c>
       <c r="E11" t="n">
-        <v>2.9027</v>
+        <v>3.784700000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>5.518199999999999</v>
+        <v>5.5182</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.654700000000001</v>
+        <v>-5.6547</v>
       </c>
       <c r="H11" t="n">
         <v>1.7061</v>
       </c>
       <c r="I11" t="n">
-        <v>-7.360700000000001</v>
+        <v>-7.3607</v>
       </c>
       <c r="J11" t="n">
         <v>-3.5855</v>
@@ -1297,7 +1297,7 @@
         <v>-2.0693</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.01530000000000031</v>
+        <v>-0.01530000000000009</v>
       </c>
       <c r="O11" t="n">
         <v>-2.0539</v>
@@ -1312,13 +1312,13 @@
         <v>15.096</v>
       </c>
       <c r="S11" t="n">
-        <v>3.774</v>
+        <v>4.655799999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>5.4722</v>
+        <v>6.354000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.698299999999999</v>
+        <v>-1.6983</v>
       </c>
       <c r="V11" t="n">
         <v>8.4146</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.3999</v>
+        <v>4.0806</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8198</v>
+        <v>1.2095</v>
       </c>
       <c r="F12" t="n">
-        <v>2.5801</v>
+        <v>2.8711</v>
       </c>
       <c r="G12" t="n">
         <v>3.0513</v>
@@ -1390,13 +1390,13 @@
         <v>1.5096</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.161</v>
+        <v>-0.4803</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7055</v>
+        <v>-0.3157</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4556</v>
+        <v>-0.1646</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.8027</v>
+        <v>3.6206</v>
       </c>
       <c r="E13" t="n">
-        <v>1.6022</v>
+        <v>2.1868</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2005</v>
+        <v>1.4338</v>
       </c>
       <c r="G13" t="n">
         <v>2.8955</v>
@@ -1468,13 +1468,13 @@
         <v>2.4531</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.5642</v>
+        <v>-0.7463</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4645</v>
+        <v>0.1201</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.0997</v>
+        <v>-0.8663999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>1.8488</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9923</v>
+        <v>1.3954</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8269</v>
+        <v>1.314</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1654</v>
+        <v>0.0813</v>
       </c>
       <c r="G15" t="n">
         <v>3.318</v>
@@ -1624,13 +1624,13 @@
         <v>2.2644</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8353</v>
+        <v>-0.4322</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.053</v>
+        <v>0.4342</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7823</v>
+        <v>-0.8663999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>-1.8678</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. ARTIGUES DAÑOBEITIA</t>
+          <t>A. SUCH LOPEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6339</v>
+        <v>0.8034</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6339</v>
+        <v>-0.5014999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>1.3049</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6339</v>
+        <v>1.5884</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6339</v>
+        <v>1.2052</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>0.3832</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6339</v>
+        <v>0.8418</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6339</v>
+        <v>0.7184</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>0.1234</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>0.7466</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>0.4868</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>0.2598</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-1.6983</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>0.1887</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-0.0301</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>-0.0789</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>0.0488</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.9434</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.6226</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.3208</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. SUCH LOPEZ</t>
+          <t>J. ARTIGUES DAÑOBEITIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5208</v>
+        <v>0.6339</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5989</v>
+        <v>0.6339</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1197</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>1.5884</v>
+        <v>0.6339</v>
       </c>
       <c r="H17" t="n">
-        <v>1.2052</v>
+        <v>0.6339</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3832</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8418</v>
+        <v>0.6339</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7184</v>
+        <v>0.6339</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1234</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7466</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4868</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2598</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.6983</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.1887</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3127</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1764</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1364</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9434</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.6226</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3208</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3074</v>
+        <v>-0.6995</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2045</v>
+        <v>0.8148</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.5119</v>
+        <v>-1.5142</v>
       </c>
       <c r="G18" t="n">
         <v>-0.0203</v>
@@ -1858,13 +1858,13 @@
         <v>1.1322</v>
       </c>
       <c r="S18" t="n">
-        <v>0.147</v>
+        <v>-0.2451</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8905</v>
+        <v>0.5008</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7435</v>
+        <v>-0.7459</v>
       </c>
       <c r="V18" t="n">
         <v>0.3208</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. POU CAMPILLO</t>
+          <t>D. CAMEROS JUAN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1681</v>
+        <v>-1.0255</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7844</v>
+        <v>-2.5113</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.9525</v>
+        <v>1.4858</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3681</v>
+        <v>-0.0141</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2512</v>
+        <v>-0.4234</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1169</v>
+        <v>0.4093</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5511</v>
+        <v>0.0732</v>
       </c>
       <c r="K19" t="n">
-        <v>0.09</v>
+        <v>0.0321</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.641</v>
+        <v>0.0411</v>
       </c>
       <c r="M19" t="n">
-        <v>0.9191</v>
+        <v>-0.0873</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1612</v>
+        <v>-0.4555</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7579</v>
+        <v>0.3682</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.3774</v>
+        <v>-0.5661</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9435</v>
+        <v>-1.887</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5661</v>
+        <v>1.3209</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0864</v>
+        <v>0.1963</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1735</v>
+        <v>-0.0559</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2599</v>
+        <v>0.2522</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2452</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>2.4524</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="X19" t="n">
-        <v>-3.6976</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. CAMEROS JUAN</t>
+          <t>A. POU CAMPILLO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1842</v>
+        <v>-1.1872</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.5113</v>
+        <v>0.9792999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3271</v>
+        <v>-2.1665</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0141</v>
+        <v>0.3681</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4234</v>
+        <v>0.2512</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4093</v>
+        <v>0.1169</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0732</v>
+        <v>-0.5511</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0321</v>
+        <v>0.09</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0411</v>
+        <v>-0.641</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0873</v>
+        <v>0.9191</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4555</v>
+        <v>0.1612</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3682</v>
+        <v>0.7579</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.5661</v>
+        <v>-0.3774</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3209</v>
+        <v>0.5661</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0376</v>
+        <v>0.0673</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0559</v>
+        <v>0.0214</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0935</v>
+        <v>0.0459</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6415999999999999</v>
+        <v>-1.2452</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.6415999999999999</v>
+        <v>2.4524</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-3.6976</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5387</v>
+        <v>-1.4305</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7298</v>
+        <v>-1.1195</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8089</v>
+        <v>-0.311</v>
       </c>
       <c r="G21" t="n">
         <v>-1.3884</v>
@@ -2092,13 +2092,13 @@
         <v>1.3209</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5467</v>
+        <v>-0.4385</v>
       </c>
       <c r="T21" t="n">
-        <v>0.9493</v>
+        <v>0.5596</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.496</v>
+        <v>-0.9981</v>
       </c>
       <c r="V21" t="n">
         <v>-0.9244</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4531</v>
+        <v>-3.3942</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4343</v>
+        <v>0.3369</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.8875</v>
+        <v>-3.7311</v>
       </c>
       <c r="G22" t="n">
         <v>1.5167</v>
@@ -2170,13 +2170,13 @@
         <v>0.3774</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3474</v>
+        <v>-0.2885</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0617</v>
+        <v>-0.0357</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4091</v>
+        <v>-0.2527</v>
       </c>
       <c r="V22" t="n">
         <v>-4.9998</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.7109</v>
+        <v>-5.0826</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.4613</v>
+        <v>-4.7536</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2496</v>
+        <v>-0.3289</v>
       </c>
       <c r="G23" t="n">
         <v>-4.8417</v>
@@ -2248,13 +2248,13 @@
         <v>0.9435</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4326</v>
+        <v>0.061</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2997</v>
+        <v>0.0074</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1329</v>
+        <v>0.0535</v>
       </c>
       <c r="V23" t="n">
         <v>-0.3018</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.9758</v>
+        <v>-6.4041</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.7888</v>
+        <v>-5.3734</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.187</v>
+        <v>-1.0306</v>
       </c>
       <c r="G24" t="n">
         <v>-3.0203</v>
@@ -2326,13 +2326,13 @@
         <v>1.1322</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2898</v>
+        <v>-0.1384</v>
       </c>
       <c r="T24" t="n">
-        <v>1.1257</v>
+        <v>0.5411</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.8359</v>
+        <v>-0.6795</v>
       </c>
       <c r="V24" t="n">
         <v>-1.547</v>
@@ -2359,22 +2359,22 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.420799999999998</v>
+        <v>-7.121900000000001</v>
       </c>
       <c r="E25" t="n">
         <v>-5.216299999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.2046</v>
+        <v>-1.905400000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>5.6549</v>
+        <v>5.654899999999996</v>
       </c>
       <c r="H25" t="n">
         <v>-1.706</v>
       </c>
       <c r="I25" t="n">
-        <v>7.361000000000002</v>
+        <v>7.361000000000001</v>
       </c>
       <c r="J25" t="n">
         <v>2.0692</v>
@@ -2383,7 +2383,7 @@
         <v>0.01539999999999997</v>
       </c>
       <c r="L25" t="n">
-        <v>2.053900000000001</v>
+        <v>2.0539</v>
       </c>
       <c r="M25" t="n">
         <v>3.5854</v>
@@ -2404,13 +2404,13 @@
         <v>13.209</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.773900000000001</v>
+        <v>-2.4748</v>
       </c>
       <c r="T25" t="n">
-        <v>1.6981</v>
+        <v>1.6984</v>
       </c>
       <c r="U25" t="n">
-        <v>-5.472199999999999</v>
+        <v>-4.1732</v>
       </c>
       <c r="V25" t="n">
         <v>-8.4146</v>
